--- a/Entregables/Matriz-Riesgos-14-09.xlsx
+++ b/Entregables/Matriz-Riesgos-14-09.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://frbautneduar-my.sharepoint.com/personal/jomansilla_frba_utn_edu_ar/Documents/04-Cuarto-Año-2026/Administracion-De-Sistemas-De-Información/TPA/Entregables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{435B435B-6DCB-4B03-811B-4B9732ECF68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D4DBDE-D076-4F17-AE1A-0A64C7987874}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{435B435B-6DCB-4B03-811B-4B9732ECF68D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8B1D65E-5510-4D79-88F4-1BFD8B465D90}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lista de Riesgos" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="231">
   <si>
     <t>Id</t>
   </si>
@@ -407,15 +407,9 @@
     <t>Arquitecto Cloud / Equipo de Infraestructura</t>
   </si>
   <si>
-    <t>Implementar metodología ágil con sprints cortos y revisiones semanales de avance. Incorporar buffer de tiempo en hitos críticos y establecer criterios de aceptación por entregable.</t>
-  </si>
-  <si>
     <t>Desvío &gt; 20% respecto al cronograma planificado; bloqueos reiterados en tareas del camino crítico.</t>
   </si>
   <si>
-    <t>Líder de Proyecto / Scrum Master</t>
-  </si>
-  <si>
     <t>Diseñar un módulo de configuración de reglas de evaluación flexible que permita a cada institución definir sus propios criterios sin requerir desarrollo adicional. Documentar el modelo de configuración.</t>
   </si>
   <si>
@@ -500,12 +494,6 @@
     <t>Líder de Proyecto / Líder Técnico</t>
   </si>
   <si>
-    <t>Establecer estándares de documentación como parte de la definición de hecho (DoD) en cada sprint. Utilizar herramientas colaborativas (Confluence, Wiki) y asignar un responsable de documentación por módulo.</t>
-  </si>
-  <si>
-    <t>Documentación ausente o desactualizada al cierre de un sprint; incorporación de nuevo integrante sin documentación disponible.</t>
-  </si>
-  <si>
     <t>Líder de Proyecto / Equipo de Desarrollo</t>
   </si>
   <si>
@@ -641,9 +629,6 @@
     <t>Resultados de pruebas de estrés y carga del sistema</t>
   </si>
   <si>
-    <t>Cronograma actualizado y actas de revisión de sprint</t>
-  </si>
-  <si>
     <t>Modelo de configuración de reglas validado</t>
   </si>
   <si>
@@ -683,9 +668,6 @@
     <t>Repositorio de código y Wiki técnica (Confluence) actualizada</t>
   </si>
   <si>
-    <t>Definición de "Hecho" (DoD) incluyendo documentación</t>
-  </si>
-  <si>
     <t>Analista de Datos</t>
   </si>
   <si>
@@ -720,6 +702,21 @@
   </si>
   <si>
     <t>Planes de Acción para Riesgos de Mayor Exposición</t>
+  </si>
+  <si>
+    <t>Cronograma actualizado y actas de revisión  del proyecto.</t>
+  </si>
+  <si>
+    <t>Realizar seguimiento periódico del cronograma y del avance de los entregables. Incorporar un buffer de tiempo en hitos críticos y establecer criterios de aceptación para cada entregable.</t>
+  </si>
+  <si>
+    <t>Establecer estándares de documentación técnica y funcional para cada entregable. Utilizar herramientas colaborativas y asignar un responsable de documentación por módulo.</t>
+  </si>
+  <si>
+    <t>Documentación ausente o desactualizada al finalizar un entregable; incorporación de nuevo integrante sin documentación disponible.</t>
+  </si>
+  <si>
+    <t>Documentación técnica y funcional actualizada y asociada a los entregables correspondientes.</t>
   </si>
 </sst>
 </file>
@@ -977,6 +974,9 @@
     <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -986,6 +986,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -994,18 +1003,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1022,6 +1019,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1330,8 +1331,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="s">
-        <v>230</v>
+      <c r="A1" s="31" t="s">
+        <v>224</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -1348,8 +1349,8 @@
       <c r="N1" s="22"/>
     </row>
     <row r="2" spans="1:14" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
-        <v>229</v>
+      <c r="A2" s="30" t="s">
+        <v>223</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -1394,19 +1395,19 @@
         <v>8</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="N3" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1429,7 +1430,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>16</v>
@@ -1438,19 +1439,19 @@
         <v>17</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K4" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1473,7 +1474,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>21</v>
@@ -1482,19 +1483,19 @@
         <v>17</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1517,7 +1518,7 @@
         <v>25</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>26</v>
@@ -1526,19 +1527,19 @@
         <v>17</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K6" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1561,7 +1562,7 @@
         <v>14</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>30</v>
@@ -1570,19 +1571,19 @@
         <v>17</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K7" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1605,7 +1606,7 @@
         <v>14</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>34</v>
@@ -1614,19 +1615,19 @@
         <v>17</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="K8" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1649,7 +1650,7 @@
         <v>14</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>38</v>
@@ -1658,19 +1659,19 @@
         <v>17</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="K9" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1693,7 +1694,7 @@
         <v>25</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>42</v>
@@ -1702,19 +1703,19 @@
         <v>17</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K10" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1737,7 +1738,7 @@
         <v>14</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>46</v>
@@ -1746,19 +1747,19 @@
         <v>17</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1781,7 +1782,7 @@
         <v>14</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>50</v>
@@ -1790,19 +1791,19 @@
         <v>17</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K12" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1825,7 +1826,7 @@
         <v>54</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>55</v>
@@ -1834,19 +1835,19 @@
         <v>17</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1869,7 +1870,7 @@
         <v>14</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>59</v>
@@ -1878,19 +1879,19 @@
         <v>17</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K14" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1913,7 +1914,7 @@
         <v>14</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>63</v>
@@ -1922,19 +1923,19 @@
         <v>17</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1957,7 +1958,7 @@
         <v>54</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>67</v>
@@ -1966,19 +1967,19 @@
         <v>17</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K16" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2001,7 +2002,7 @@
         <v>25</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>71</v>
@@ -2010,19 +2011,19 @@
         <v>17</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2045,7 +2046,7 @@
         <v>14</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>76</v>
@@ -2054,19 +2055,19 @@
         <v>17</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K18" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2089,7 +2090,7 @@
         <v>14</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>80</v>
@@ -2098,19 +2099,19 @@
         <v>17</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2124,7 +2125,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>75</v>
@@ -2133,7 +2134,7 @@
         <v>14</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>83</v>
@@ -2142,19 +2143,19 @@
         <v>17</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="K20" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2177,7 +2178,7 @@
         <v>14</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>87</v>
@@ -2186,19 +2187,19 @@
         <v>17</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2221,7 +2222,7 @@
         <v>14</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>91</v>
@@ -2230,19 +2231,19 @@
         <v>17</v>
       </c>
       <c r="J22" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="K22" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="K22" s="19" t="s">
-        <v>228</v>
-      </c>
       <c r="L22" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2265,7 +2266,7 @@
         <v>14</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>95</v>
@@ -2274,19 +2275,19 @@
         <v>17</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -2309,7 +2310,7 @@
         <v>75</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>99</v>
@@ -2318,23 +2319,23 @@
         <v>17</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="K24" s="19" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="34" t="s">
         <v>100</v>
       </c>
       <c r="C26" s="22"/>
@@ -2353,9 +2354,9 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B27" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="29" t="s">
+        <v>178</v>
+      </c>
+      <c r="C27" s="33" t="s">
         <v>101</v>
       </c>
       <c r="D27" s="22"/>
@@ -2373,9 +2374,9 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="C28" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="C28" s="32" t="s">
         <v>102</v>
       </c>
       <c r="D28" s="22"/>
@@ -2393,7 +2394,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B29" s="10" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C29" s="21" t="s">
         <v>103</v>
@@ -2442,8 +2443,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
-        <v>231</v>
+      <c r="A1" s="25" t="s">
+        <v>225</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -2451,8 +2452,8 @@
       <c r="E1" s="22"/>
     </row>
     <row r="2" spans="1:5" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="31" t="s">
-        <v>229</v>
+      <c r="A2" s="29" t="s">
+        <v>223</v>
       </c>
       <c r="B2" s="22"/>
       <c r="C2" s="22"/>
@@ -2586,13 +2587,13 @@
         <v>108</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="E10" s="3" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2603,13 +2604,13 @@
         <v>108</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>130</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2617,16 +2618,16 @@
         <v>50</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2637,13 +2638,13 @@
         <v>108</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2654,13 +2655,13 @@
         <v>108</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2668,16 +2669,16 @@
         <v>63</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C15" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2688,13 +2689,13 @@
         <v>108</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2705,13 +2706,13 @@
         <v>108</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2722,13 +2723,13 @@
         <v>108</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2739,13 +2740,13 @@
         <v>108</v>
       </c>
       <c r="C19" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>155</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2756,13 +2757,13 @@
         <v>108</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>159</v>
+        <v>229</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2773,13 +2774,13 @@
         <v>108</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2787,16 +2788,16 @@
         <v>91</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2807,13 +2808,13 @@
         <v>108</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="56.1" customHeight="1" x14ac:dyDescent="0.25">
@@ -2824,18 +2825,18 @@
         <v>108</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
-        <v>174</v>
+      <c r="B26" s="28" t="s">
+        <v>170</v>
       </c>
       <c r="C26" s="22"/>
       <c r="D26" s="22"/>
@@ -2846,8 +2847,8 @@
       <c r="B27" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="C27" s="26" t="s">
-        <v>175</v>
+      <c r="C27" s="27" t="s">
+        <v>171</v>
       </c>
       <c r="D27" s="22"/>
       <c r="E27" s="22"/>
@@ -2855,10 +2856,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>176</v>
+        <v>131</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>172</v>
       </c>
       <c r="D28" s="22"/>
       <c r="E28" s="22"/>
@@ -2866,10 +2867,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D29" s="22"/>
       <c r="E29" s="22"/>
@@ -2877,10 +2878,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B30" s="10" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
@@ -2888,10 +2889,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B31" s="18" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C31" s="24" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D31" s="24"/>
       <c r="E31" s="24"/>
